--- a/equipo/D3/CONSULTAS_AUDIT_D3_20260901.XLSX
+++ b/equipo/D3/CONSULTAS_AUDIT_D3_20260901.XLSX
@@ -107,17 +107,17 @@
       </c>
       <c r="E2" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bases Técnicas Transversales, sección 5.4, pág. 13 (RT-05.29); Bases Técnicas Caso 10, Capítulos 14.2 y 15, págs. 30 y 31</t>
+          <t xml:space="preserve">Bases Técnicas Caso 10: criterio de aceptación 17 (Cap. 18, pág. 41); parámetro RT-05.29 (Cap. 15, pág. 31); sección B.1 (Cap. B, pág. 46); sección 7.3 (Cap. 7, pág. 15)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">El requisito RT-05.29 establece que la latencia máxima entre la ocurrencia de una transacción y su disponibilidad en la capa analítica será la que fije el caso y, en su defecto, no superará las cuatro horas. El caso no fija un valor explícito para esta latencia, pero establece que el dispositivo a bordo debe operar 72 horas sin cobertura y que la reconexión de cientos de unidades será simultánea (numeral 14.2). Durante esas 72 horas la transacción existe en el dispositivo y no en el sistema central. Sírvase precisar si la latencia de cuatro horas se mide desde la ocurrencia de la transacción en el dispositivo o desde su llegada efectiva al sistema central tras la reconexión.</t>
+          <t xml:space="preserve">El criterio de aceptación 17 (pág. 41) establece que el costo por viaje estará disponible dentro de las 24 horas de cerrado el viaje, sin calificación. El parámetro RT-05.29 del Capítulo 15 (pág. 31) establece, para el mismo dato, «no superior a 24 horas tras su cierre, con los componentes que a esa fecha estén disponibles y con indicación explícita de los que aún no lo están». La sección B.1 (pág. 46) reproduce la misma calificación. El Capítulo 7.3 registra que el consumo de combustible llega con hasta 40 días de desfase y los peajes se liquidan mensualmente. Dado que el criterio 17 y el parámetro RT-05.29 describen el mismo dato con distinto grado de calificación, sírvase precisar si el criterio 17 se satisface con un costo preliminar trazable que declare los componentes pendientes, conforme al parámetro RT-05.29 y a la sección B.1, o si exige el costo completo y definitivo.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Se entiende que la latencia de cuatro horas se medirá desde la recepción de los datos en el sistema central. Durante la operación desconectada, los tableros indicarán explícitamente la cobertura y antigüedad de la información disponible.</t>
+          <t xml:space="preserve">Se entiende que el criterio 17 se satisface conforme a la calificación que el propio caso introduce en el parámetro RT-05.29 y en la sección B.1: un costo preliminar trazable con los componentes disponibles al cierre, que se actualiza automáticamente a medida que cada componente llega, con historial de versiones.</t>
         </is>
       </c>
     </row>
@@ -144,89 +144,15 @@
       </c>
       <c r="E3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bases Técnicas Caso 10, Capítulos 7.3 y 18, págs. 15 y 41 (criterio de aceptación 17)</t>
+          <t xml:space="preserve">Bases Técnicas Caso 10, Capítulos 5 y 7.3, págs. 12 y 15; Anexo A, pág. 45; Bases Técnicas Transversales, sección 5.3, pág. 12 (RT-05.21)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">El criterio de aceptación 17 establece que el costo por viaje estará disponible dentro de las 24 horas de cerrado el viaje. El Capítulo 7.3 registra que el consumo de combustible de la red de estaciones de servicio llega con hasta 40 días de desfase, los peajes se liquidan mensualmente y los neumáticos se controlan en planilla. Sírvase precisar si el criterio 17 admite un costo preliminar calculado con los componentes disponibles al cierre y una declaración explícita de los pendientes, o si exige el costo completo y definitivo dentro de ese plazo.</t>
+          <t xml:space="preserve">El requisito RT-05.21 exige declarar, por cada integración, el modo, el volumen esperado, la ventana de disponibilidad y el comportamiento ante indisponibilidad del sistema contraparte. El Capítulo 5 y el Anexo A identifican el portal de la red de estaciones de servicio y el sistema del dispositivo de peaje como integraciones a mantener. Respecto de estos dos sistemas, sírvase indicar si disponen de interfaz de programación, exportación de archivos u otro mecanismo de obtención de datos, el formato en que los datos se entregan, la frecuencia con que están disponibles y si existe posibilidad de acceso anticipado respecto de la liquidación mensual actual.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Se entiende que el criterio se satisface con un costo preliminar trazable, calculado con los componentes disponibles al cierre del viaje, que se actualiza automáticamente a medida que cada componente llega, manteniendo el historial de versiones y la fecha de cada actualización.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">AUDIT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">01-09-2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Técnica</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bases Técnicas Caso 10, Capítulos 14.2 y 18, págs. 30 y 41; Bases Técnicas Transversales, sección 5.1, pág. 11 (RT-05.07)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">La sección 14.2 incluye el «volumen de almacenamiento de la evidencia de jornada por el plazo de retención exigido» como dimensión que el PROPONENTE debe estimar, lo que presupone un plazo definido. El criterio de aceptación 4 exige que esa evidencia resista una alegación de manipulación y sea oponible ante la autoridad, el cliente y el seguro. Sin embargo, el caso no especifica el plazo de retención para la evidencia de jornada, a diferencia de los datos de posición y telemetría, para los cuales indica dos años en línea con política de agregación. Sírvase indicar el plazo de retención exigido para la evidencia de jornada, o confirmar que el PROPONENTE debe derivarlo de la normativa laboral aplicable y del plazo contractual.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Se aplicará el mayor entre el plazo de prescripción de las acciones laborales del régimen especial de jornada del transporte de carga y el plazo contractual de 56 meses, con la evidencia conservada a su granularidad original durante todo el período.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">AUDIT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">01-09-2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Técnica</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bases Técnicas Caso 10, Capítulos 5 y 7.3, págs. 12 y 15; Anexo A, pág. 45; Bases Técnicas Transversales, sección 5.3, pág. 12 (RT-05.21)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">El requisito RT-05.21 exige declarar, por cada integración, el modo, el volumen esperado, la ventana de disponibilidad y el comportamiento ante indisponibilidad del sistema contraparte. El Capítulo 5 y el Anexo A identifican el portal de la red de estaciones de servicio y el sistema del dispositivo de peaje como integraciones a mantener. Respecto de estos dos sistemas, sírvase indicar si disponen de interfaz de programación, exportación de archivos u otro mecanismo de obtención de datos, el formato en que los datos se entregan, la frecuencia con que están disponibles y si existe posibilidad de acceso anticipado respecto de la liquidación mensual actual.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">De no existir antecedentes adicionales, se asumirá integración por archivo con periodicidad mensual para ambos sistemas, con el desfase actual de hasta 40 días para combustible, y se diseñará la capa de integración para soportar una eventual migración a acceso anticipado si alguno de los proveedores lo habilita en el futuro.</t>
         </is>
